--- a/astro-site/public/dl/hotel-checklist-templates/15-hotel-spa-checklists.xlsx
+++ b/astro-site/public/dl/hotel-checklist-templates/15-hotel-spa-checklists.xlsx
@@ -601,7 +601,7 @@
     <row r="6">
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>▸ Covers the hot tub (whirlpool spa), sauna, steam room and the indoor heated pool.</t>
+          <t>▸ Covers the hot tub (whirlpool spa), sauna, steam room and treatment rooms; an indoor heated pool uses the pool checklists in file 11.</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Check hot tub / pool temperature (target 95–100 °F, never above 104 °F, MAHC 2024) and adjust; post the hot tub sign (104 °F, no children under 5, no alcohol, pregnancy and heart conditions); hot tub free chlorine at least 3.0 ppm</t>
+          <t>Check hot tub (whirlpool spa) temperature (target 95–100 °F, never above 104 °F, MAHC 2024) and adjust; post the hot tub sign (104 °F, no children under 5, no alcohol, pregnancy and heart conditions); hot tub free chlorine at least 3.0 ppm</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Turn off saunas, steam room and hot tub</t>
+          <t>Turn off saunas and steam room; on the hot tub switch off only the jets and air blower: filtration, circulation and disinfection keep running 24 hours a day (MAHC 2024 §5.12.1.1)</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
